--- a/dataproduct.api/wwwroot/templates/HRC1_BBXNSL_PhoiTam.xlsx
+++ b/dataproduct.api/wwwroot/templates/HRC1_BBXNSL_PhoiTam.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\_Projects\BIEUMAU_SANXUAT\Source\dataproduct.BE\dataproduct.api\wwwroot\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{197B2C8C-8EC2-4A2C-8589-B24D742C71B1}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24CAFCFD-52B1-4ACE-8B8A-DDAA8AF49697}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="24720" windowHeight="11805" xr2:uid="{8D26054B-D371-44B9-99F0-3A3B1380D846}"/>
   </bookViews>
@@ -184,182 +184,43 @@
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>100853</xdr:rowOff>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>1645583</xdr:colOff>
+      <xdr:colOff>1176306</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>896471</xdr:rowOff>
+      <xdr:rowOff>724001</xdr:rowOff>
     </xdr:to>
-    <xdr:grpSp>
-      <xdr:nvGrpSpPr>
-        <xdr:cNvPr id="5" name="Group 3">
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{976BAF94-83FC-4DC9-B6CA-321EF35DD714}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D0474B14-A904-414B-BB70-912052C02B55}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
-        <xdr:cNvGrpSpPr>
-          <a:grpSpLocks noChangeAspect="1"/>
-        </xdr:cNvGrpSpPr>
-      </xdr:nvGrpSpPr>
-      <xdr:grpSpPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
         <a:xfrm>
-          <a:off x="0" y="100853"/>
-          <a:ext cx="2250701" cy="795618"/>
-          <a:chOff x="3630740" y="5047981"/>
-          <a:chExt cx="2095500" cy="876300"/>
+          <a:off x="0" y="0"/>
+          <a:ext cx="1781424" cy="724001"/>
         </a:xfrm>
-      </xdr:grpSpPr>
-      <xdr:pic>
-        <xdr:nvPicPr>
-          <xdr:cNvPr id="6" name="Picture 6">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{26A0C954-C2D4-46A6-87B3-19A59D284078}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvPicPr>
-            <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
-          </xdr:cNvPicPr>
-        </xdr:nvPicPr>
-        <xdr:blipFill>
-          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
-            <a:extLst>
-              <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-                <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-              </a:ext>
-            </a:extLst>
-          </a:blip>
-          <a:srcRect/>
-          <a:stretch>
-            <a:fillRect/>
-          </a:stretch>
-        </xdr:blipFill>
-        <xdr:spPr>
-          <a:xfrm>
-            <a:off x="3764090" y="5047981"/>
-            <a:ext cx="1819275" cy="407343"/>
-          </a:xfrm>
-          <a:prstGeom prst="rect">
-            <a:avLst/>
-          </a:prstGeom>
-          <a:noFill/>
-          <a:ln>
-            <a:noFill/>
-          </a:ln>
-          <a:extLst>
-            <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-              <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-                <a:solidFill>
-                  <a:srgbClr val="FFFFFF"/>
-                </a:solidFill>
-              </a14:hiddenFill>
-            </a:ext>
-            <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-              <a14:hiddenLine xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" w="9525">
-                <a:solidFill>
-                  <a:srgbClr val="000000"/>
-                </a:solidFill>
-                <a:miter lim="800000"/>
-                <a:headEnd/>
-                <a:tailEnd/>
-              </a14:hiddenLine>
-            </a:ext>
-          </a:extLst>
-        </xdr:spPr>
-      </xdr:pic>
-      <xdr:sp macro="" textlink="">
-        <xdr:nvSpPr>
-          <xdr:cNvPr id="7" name="TextBox 4">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{14FDA956-39EE-4520-9E62-1C3DA85F10F1}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvSpPr txBox="1">
-            <a:spLocks noChangeArrowheads="1"/>
-          </xdr:cNvSpPr>
-        </xdr:nvSpPr>
-        <xdr:spPr>
-          <a:xfrm>
-            <a:off x="3630740" y="5430197"/>
-            <a:ext cx="2095500" cy="494084"/>
-          </a:xfrm>
-          <a:prstGeom prst="rect">
-            <a:avLst/>
-          </a:prstGeom>
-          <a:noFill/>
-          <a:ln>
-            <a:noFill/>
-          </a:ln>
-        </xdr:spPr>
-        <xdr:txBody>
-          <a:bodyPr rot="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" anchor="ctr" anchorCtr="0" upright="1">
-            <a:noAutofit/>
-          </a:bodyPr>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr marL="0" marR="0" algn="ctr">
-              <a:lnSpc>
-                <a:spcPts val="1200"/>
-              </a:lnSpc>
-              <a:spcBef>
-                <a:spcPts val="0"/>
-              </a:spcBef>
-              <a:spcAft>
-                <a:spcPts val="800"/>
-              </a:spcAft>
-            </a:pPr>
-            <a:r>
-              <a:rPr lang="en-US" sz="1200" b="1">
-                <a:solidFill>
-                  <a:srgbClr val="000000"/>
-                </a:solidFill>
-                <a:effectLst/>
-                <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-                <a:ea typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
-                <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-              </a:rPr>
-              <a:t>CÔNG TY CỔ PHẦN THÉP</a:t>
-            </a:r>
-            <a:br>
-              <a:rPr lang="en-US" sz="1200" b="1">
-                <a:solidFill>
-                  <a:srgbClr val="000000"/>
-                </a:solidFill>
-                <a:effectLst/>
-                <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-                <a:ea typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
-                <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-              </a:rPr>
-            </a:br>
-            <a:r>
-              <a:rPr lang="en-US" sz="1200" b="1">
-                <a:solidFill>
-                  <a:srgbClr val="000000"/>
-                </a:solidFill>
-                <a:effectLst/>
-                <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-                <a:ea typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
-                <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-              </a:rPr>
-              <a:t>HÒA PHÁT DUNG QUẤT</a:t>
-            </a:r>
-            <a:endParaRPr lang="en-US" sz="1100">
-              <a:effectLst/>
-              <a:latin typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
-              <a:ea typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
-              <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-            </a:endParaRPr>
-          </a:p>
-        </xdr:txBody>
-      </xdr:sp>
-    </xdr:grpSp>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>

--- a/dataproduct.api/wwwroot/templates/HRC1_BBXNSL_PhoiTam.xlsx
+++ b/dataproduct.api/wwwroot/templates/HRC1_BBXNSL_PhoiTam.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\_Projects\BIEUMAU_SANXUAT\Source\dataproduct.BE\dataproduct.api\wwwroot\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24CAFCFD-52B1-4ACE-8B8A-DDAA8AF49697}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE571B38-31BC-4748-8303-702417FADDFF}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="24720" windowHeight="11805" xr2:uid="{8D26054B-D371-44B9-99F0-3A3B1380D846}"/>
   </bookViews>
@@ -25,18 +25,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
-  <si>
-    <t>Mác thép</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
   <si>
     <t>Ghi chú</t>
   </si>
   <si>
     <t>STT</t>
-  </si>
-  <si>
-    <t>Sản phẩm</t>
   </si>
   <si>
     <t>Số phôi</t>
@@ -51,6 +45,9 @@
   </si>
   <si>
     <t xml:space="preserve">BIÊN BẢN XÁC NHẬN SẢN LƯỢNG PHÔI TẤM </t>
+  </si>
+  <si>
+    <t>Sản phẩm x Mác thép</t>
   </si>
 </sst>
 </file>
@@ -106,7 +103,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -138,16 +135,32 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
@@ -523,84 +536,76 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1FE70C8B-98CB-4803-B542-3EE340B9292E}">
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:E5"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="2"/>
     <col min="2" max="2" width="38.5703125" style="2" customWidth="1"/>
-    <col min="3" max="3" width="35.28515625" style="2" customWidth="1"/>
-    <col min="4" max="4" width="17.28515625" style="2" customWidth="1"/>
-    <col min="5" max="5" width="33.5703125" style="2" customWidth="1"/>
-    <col min="6" max="6" width="35.140625" style="2" customWidth="1"/>
-    <col min="7" max="7" width="14.7109375" style="2" customWidth="1"/>
-    <col min="8" max="8" width="15.85546875" style="2" customWidth="1"/>
-    <col min="9" max="10" width="9.140625" style="2"/>
-    <col min="11" max="11" width="13.140625" style="2" customWidth="1"/>
-    <col min="12" max="12" width="13.42578125" style="2" customWidth="1"/>
-    <col min="13" max="13" width="12.7109375" style="2" customWidth="1"/>
-    <col min="14" max="16384" width="9.140625" style="2"/>
+    <col min="3" max="3" width="17.28515625" style="2" customWidth="1"/>
+    <col min="4" max="4" width="33.5703125" style="2" customWidth="1"/>
+    <col min="5" max="5" width="35.140625" style="2" customWidth="1"/>
+    <col min="6" max="6" width="14.7109375" style="2" customWidth="1"/>
+    <col min="7" max="7" width="15.85546875" style="2" customWidth="1"/>
+    <col min="8" max="9" width="9.140625" style="2"/>
+    <col min="10" max="10" width="13.140625" style="2" customWidth="1"/>
+    <col min="11" max="11" width="13.42578125" style="2" customWidth="1"/>
+    <col min="12" max="12" width="12.7109375" style="2" customWidth="1"/>
+    <col min="13" max="16384" width="9.140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="78.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="3" t="s">
+    <row r="1" spans="1:5" ht="78.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B1" s="5"/>
+      <c r="C1" s="5"/>
+      <c r="D1" s="5"/>
+      <c r="E1" s="5"/>
+    </row>
+    <row r="2" spans="1:5" ht="33" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" s="6"/>
+      <c r="C2" s="6"/>
+      <c r="D2" s="6"/>
+      <c r="E2" s="6"/>
+    </row>
+    <row r="3" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="6"/>
+      <c r="B3" s="6"/>
+      <c r="C3" s="6"/>
+      <c r="D3" s="6"/>
+      <c r="E3" s="6"/>
+    </row>
+    <row r="4" spans="1:5" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="7"/>
+      <c r="B4" s="7"/>
+      <c r="C4" s="7"/>
+      <c r="D4" s="7"/>
+      <c r="E4" s="7"/>
+    </row>
+    <row r="5" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B5" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B1" s="4"/>
-      <c r="C1" s="4"/>
-      <c r="D1" s="4"/>
-      <c r="E1" s="4"/>
-      <c r="F1" s="4"/>
-    </row>
-    <row r="2" spans="1:6" ht="33" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="B2" s="5"/>
-      <c r="C2" s="5"/>
-      <c r="D2" s="5"/>
-      <c r="E2" s="5"/>
-      <c r="F2" s="5"/>
-    </row>
-    <row r="3" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="5"/>
-      <c r="B3" s="5"/>
-      <c r="C3" s="5"/>
-      <c r="D3" s="5"/>
-      <c r="E3" s="5"/>
-      <c r="F3" s="5"/>
-    </row>
-    <row r="4" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="6"/>
-      <c r="B4" s="6"/>
-      <c r="C4" s="6"/>
-      <c r="D4" s="6"/>
-      <c r="E4" s="6"/>
-      <c r="F4" s="6"/>
-    </row>
-    <row r="5" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
+      <c r="C5" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="D5" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="E5" s="1" t="s">
         <v>0</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>1</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A2:F4"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A2:E4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>

--- a/dataproduct.api/wwwroot/templates/HRC1_BBXNSL_PhoiTam.xlsx
+++ b/dataproduct.api/wwwroot/templates/HRC1_BBXNSL_PhoiTam.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\_Projects\BIEUMAU_SANXUAT\Source\dataproduct.BE\dataproduct.api\wwwroot\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE571B38-31BC-4748-8303-702417FADDFF}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A46A147-A16A-4CBC-A54E-A7A6E39ADF79}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="24720" windowHeight="11805" xr2:uid="{8D26054B-D371-44B9-99F0-3A3B1380D846}"/>
   </bookViews>
@@ -54,7 +54,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -88,6 +88,14 @@
       <name val="Times New Roman"/>
       <family val="1"/>
     </font>
+    <font>
+      <b/>
+      <i/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -152,7 +160,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -170,7 +178,10 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -572,18 +583,18 @@
       <c r="E2" s="6"/>
     </row>
     <row r="3" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="6"/>
-      <c r="B3" s="6"/>
-      <c r="C3" s="6"/>
-      <c r="D3" s="6"/>
-      <c r="E3" s="6"/>
+      <c r="A3" s="7"/>
+      <c r="B3" s="7"/>
+      <c r="C3" s="7"/>
+      <c r="D3" s="7"/>
+      <c r="E3" s="7"/>
     </row>
     <row r="4" spans="1:5" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="7"/>
-      <c r="B4" s="7"/>
-      <c r="C4" s="7"/>
-      <c r="D4" s="7"/>
-      <c r="E4" s="7"/>
+      <c r="A4" s="8"/>
+      <c r="B4" s="8"/>
+      <c r="C4" s="8"/>
+      <c r="D4" s="8"/>
+      <c r="E4" s="8"/>
     </row>
     <row r="5" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
@@ -603,9 +614,11 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="4">
     <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A2:E4"/>
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A3:E3"/>
+    <mergeCell ref="A4:E4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>

--- a/dataproduct.api/wwwroot/templates/HRC1_BBXNSL_PhoiTam.xlsx
+++ b/dataproduct.api/wwwroot/templates/HRC1_BBXNSL_PhoiTam.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\_Projects\BIEUMAU_SANXUAT\Source\dataproduct.BE\dataproduct.api\wwwroot\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A46A147-A16A-4CBC-A54E-A7A6E39ADF79}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3CD1057-D019-458C-95B5-72E9CDA4C2E0}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="24720" windowHeight="11805" xr2:uid="{8D26054B-D371-44B9-99F0-3A3B1380D846}"/>
   </bookViews>
@@ -83,15 +83,15 @@
     </font>
     <font>
       <b/>
-      <sz val="26"/>
+      <i/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Times New Roman"/>
       <family val="1"/>
     </font>
     <font>
       <b/>
-      <i/>
-      <sz val="11"/>
+      <sz val="18"/>
       <color theme="1"/>
       <name val="Times New Roman"/>
       <family val="1"/>
@@ -178,10 +178,10 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -574,27 +574,27 @@
       <c r="E1" s="5"/>
     </row>
     <row r="2" spans="1:5" ht="33" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="6" t="s">
+      <c r="A2" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="6"/>
-      <c r="C2" s="6"/>
-      <c r="D2" s="6"/>
-      <c r="E2" s="6"/>
+      <c r="B2" s="8"/>
+      <c r="C2" s="8"/>
+      <c r="D2" s="8"/>
+      <c r="E2" s="8"/>
     </row>
     <row r="3" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="7"/>
-      <c r="B3" s="7"/>
-      <c r="C3" s="7"/>
-      <c r="D3" s="7"/>
-      <c r="E3" s="7"/>
+      <c r="A3" s="6"/>
+      <c r="B3" s="6"/>
+      <c r="C3" s="6"/>
+      <c r="D3" s="6"/>
+      <c r="E3" s="6"/>
     </row>
     <row r="4" spans="1:5" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="8"/>
-      <c r="B4" s="8"/>
-      <c r="C4" s="8"/>
-      <c r="D4" s="8"/>
-      <c r="E4" s="8"/>
+      <c r="A4" s="7"/>
+      <c r="B4" s="7"/>
+      <c r="C4" s="7"/>
+      <c r="D4" s="7"/>
+      <c r="E4" s="7"/>
     </row>
     <row r="5" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
